--- a/out/07_Before_vs_After.xlsx
+++ b/out/07_Before_vs_After.xlsx
@@ -33,12 +33,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -504,25 +499,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>331</v>
+        <v>257</v>
       </c>
       <c r="D2" t="n">
-        <v>411</v>
+        <v>320</v>
       </c>
       <c r="E2" t="n">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="F2" t="n">
-        <v>192151</v>
+        <v>193641</v>
       </c>
       <c r="G2" t="n">
-        <v>4807982.49</v>
+        <v>4866058.59</v>
       </c>
       <c r="H2" t="n">
-        <v>13826</v>
+        <v>10735</v>
       </c>
       <c r="I2" t="n">
-        <v>34964</v>
+        <v>27147</v>
       </c>
     </row>
     <row r="3">
@@ -537,25 +532,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D3" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="E3" t="n">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="F3" t="n">
-        <v>192823</v>
+        <v>194296</v>
       </c>
       <c r="G3" t="n">
-        <v>4826245.77</v>
+        <v>4884558.04</v>
       </c>
       <c r="H3" t="n">
-        <v>3133</v>
+        <v>2339</v>
       </c>
       <c r="I3" t="n">
-        <v>7922</v>
+        <v>5915</v>
       </c>
     </row>
     <row r="4">
@@ -570,25 +565,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="F4" t="n">
-        <v>192837</v>
+        <v>194310</v>
       </c>
       <c r="G4" t="n">
-        <v>4826575.63</v>
+        <v>4884870.9</v>
       </c>
       <c r="H4" t="n">
-        <v>794</v>
+        <v>585</v>
       </c>
       <c r="I4" t="n">
-        <v>2007</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="5">
@@ -603,25 +598,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="F5" t="n">
-        <v>192838</v>
+        <v>194313</v>
       </c>
       <c r="G5" t="n">
-        <v>4826575.62</v>
+        <v>4884946.87</v>
       </c>
       <c r="H5" t="n">
-        <v>376</v>
+        <v>334</v>
       </c>
       <c r="I5" t="n">
-        <v>951</v>
+        <v>845</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +640,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>193005</v>
+        <v>194447</v>
       </c>
       <c r="G6" t="n">
-        <v>4830995.95</v>
+        <v>4888451.53</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1611,7 +1606,7 @@
         <v>55</v>
       </c>
       <c r="M22" t="n">
-        <v>2589</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="23">
@@ -1734,7 +1729,7 @@
         <v>44</v>
       </c>
       <c r="M25" t="n">
-        <v>6633</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="26">
@@ -1939,7 +1934,7 @@
         <v>84</v>
       </c>
       <c r="M30" t="n">
-        <v>9902</v>
+        <v>10361</v>
       </c>
     </row>
     <row r="31">
@@ -1980,7 +1975,7 @@
         <v>37</v>
       </c>
       <c r="M31" t="n">
-        <v>19413</v>
+        <v>19458</v>
       </c>
     </row>
     <row r="32">
@@ -2249,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="H38" t="n">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="I38" t="n">
-        <v>78353.73</v>
+        <v>78370.72</v>
       </c>
       <c r="J38" t="n">
         <v>24</v>
@@ -2308,7 +2303,7 @@
         <v>43</v>
       </c>
       <c r="M39" t="n">
-        <v>8929</v>
+        <v>9388</v>
       </c>
     </row>
     <row r="40">
@@ -2349,7 +2344,7 @@
         <v>39</v>
       </c>
       <c r="M40" t="n">
-        <v>10022</v>
+        <v>10181</v>
       </c>
     </row>
     <row r="41">
@@ -2357,7 +2352,7 @@
         <v>46243</v>
       </c>
       <c r="B41" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -2372,13 +2367,13 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>2513</v>
+        <v>2527</v>
       </c>
       <c r="H41" t="n">
-        <v>3246</v>
+        <v>3260</v>
       </c>
       <c r="I41" t="n">
-        <v>80306.53999999999</v>
+        <v>81146.39999999999</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
@@ -2387,10 +2382,10 @@
         <v>113</v>
       </c>
       <c r="L41" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M41" t="n">
-        <v>8113</v>
+        <v>8254</v>
       </c>
     </row>
     <row r="42">
@@ -2398,10 +2393,10 @@
         <v>46244</v>
       </c>
       <c r="B42" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2413,13 +2408,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>2590</v>
+        <v>2621</v>
       </c>
       <c r="H42" t="n">
-        <v>3310</v>
+        <v>3351</v>
       </c>
       <c r="I42" t="n">
-        <v>82225.89999999999</v>
+        <v>83645.49000000001</v>
       </c>
       <c r="J42" t="n">
         <v>23</v>
@@ -2428,10 +2423,10 @@
         <v>88</v>
       </c>
       <c r="L42" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M42" t="n">
-        <v>7222</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="43">
@@ -2442,7 +2437,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2454,13 +2449,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>2411</v>
+        <v>2421</v>
       </c>
       <c r="H43" t="n">
-        <v>3123</v>
+        <v>3135</v>
       </c>
       <c r="I43" t="n">
-        <v>76558.77</v>
+        <v>77148.64999999999</v>
       </c>
       <c r="J43" t="n">
         <v>23</v>
@@ -2469,10 +2464,10 @@
         <v>87</v>
       </c>
       <c r="L43" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M43" t="n">
-        <v>8886</v>
+        <v>9105</v>
       </c>
     </row>
     <row r="44">
@@ -2480,13 +2475,13 @@
         <v>46246</v>
       </c>
       <c r="B44" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -2495,13 +2490,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>2548</v>
+        <v>2616</v>
       </c>
       <c r="H44" t="n">
-        <v>3204</v>
+        <v>3294</v>
       </c>
       <c r="I44" t="n">
-        <v>76937.96000000001</v>
+        <v>80127.06</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
@@ -2510,7 +2505,7 @@
         <v>84</v>
       </c>
       <c r="L44" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M44" t="n">
         <v>8236</v>
@@ -2521,10 +2516,10 @@
         <v>46247</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -2536,22 +2531,22 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>2487</v>
+        <v>2548</v>
       </c>
       <c r="H45" t="n">
-        <v>3179</v>
+        <v>3257</v>
       </c>
       <c r="I45" t="n">
-        <v>78126.21000000001</v>
+        <v>80985.42999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K45" t="n">
         <v>76</v>
       </c>
       <c r="L45" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M45" t="n">
         <v>9192</v>
@@ -2562,7 +2557,7 @@
         <v>46248</v>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -2577,13 +2572,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>2571</v>
+        <v>2625</v>
       </c>
       <c r="H46" t="n">
-        <v>3277</v>
+        <v>3351</v>
       </c>
       <c r="I46" t="n">
-        <v>81481.23</v>
+        <v>84126.49000000001</v>
       </c>
       <c r="J46" t="n">
         <v>24</v>
@@ -2618,13 +2613,13 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>2412</v>
+        <v>2469</v>
       </c>
       <c r="H47" t="n">
-        <v>3067</v>
+        <v>3136</v>
       </c>
       <c r="I47" t="n">
-        <v>76965.33</v>
+        <v>79362.64</v>
       </c>
       <c r="J47" t="n">
         <v>23</v>
@@ -2644,10 +2639,10 @@
         <v>46250</v>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2659,25 +2654,25 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>2764</v>
+        <v>2776</v>
       </c>
       <c r="H48" t="n">
-        <v>3478</v>
+        <v>3495</v>
       </c>
       <c r="I48" t="n">
-        <v>83965.22</v>
+        <v>84647.05</v>
       </c>
       <c r="J48" t="n">
         <v>23</v>
       </c>
       <c r="K48" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M48" t="n">
-        <v>7450</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="49">
@@ -2685,13 +2680,13 @@
         <v>46251</v>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -2700,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>2397</v>
+        <v>2485</v>
       </c>
       <c r="H49" t="n">
-        <v>3037</v>
+        <v>3152</v>
       </c>
       <c r="I49" t="n">
-        <v>77114.63</v>
+        <v>81683.48</v>
       </c>
       <c r="J49" t="n">
         <v>23</v>
@@ -2715,10 +2710,10 @@
         <v>83</v>
       </c>
       <c r="L49" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M49" t="n">
-        <v>6123</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="50">
@@ -2741,13 +2736,13 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>2589</v>
+        <v>2666</v>
       </c>
       <c r="H50" t="n">
-        <v>3301</v>
+        <v>3394</v>
       </c>
       <c r="I50" t="n">
-        <v>83215.99000000001</v>
+        <v>86667.06</v>
       </c>
       <c r="J50" t="n">
         <v>22</v>
@@ -2756,7 +2751,7 @@
         <v>97</v>
       </c>
       <c r="L50" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M50" t="n">
         <v>6511</v>
@@ -2782,13 +2777,13 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>2390</v>
+        <v>2426</v>
       </c>
       <c r="H51" t="n">
-        <v>3057</v>
+        <v>3100</v>
       </c>
       <c r="I51" t="n">
-        <v>76475.42999999999</v>
+        <v>79070</v>
       </c>
       <c r="J51" t="n">
         <v>23</v>
@@ -2797,10 +2792,10 @@
         <v>80</v>
       </c>
       <c r="L51" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M51" t="n">
-        <v>6901</v>
+        <v>6899</v>
       </c>
     </row>
     <row r="52">
@@ -2823,16 +2818,16 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>2581</v>
+        <v>2618</v>
       </c>
       <c r="H52" t="n">
-        <v>3332</v>
+        <v>3379</v>
       </c>
       <c r="I52" t="n">
-        <v>82357.67999999999</v>
+        <v>84355.21000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
         <v>66</v>
@@ -2849,10 +2844,10 @@
         <v>46255</v>
       </c>
       <c r="B53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2864,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>2568</v>
+        <v>2627</v>
       </c>
       <c r="H53" t="n">
-        <v>3297</v>
+        <v>3370</v>
       </c>
       <c r="I53" t="n">
-        <v>82944.03</v>
+        <v>86141.3</v>
       </c>
       <c r="J53" t="n">
         <v>23</v>
@@ -2879,10 +2874,10 @@
         <v>78</v>
       </c>
       <c r="L53" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M53" t="n">
-        <v>5144</v>
+        <v>5189</v>
       </c>
     </row>
     <row r="54">
@@ -2890,40 +2885,40 @@
         <v>46256</v>
       </c>
       <c r="B54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>2479</v>
+        <v>2534</v>
       </c>
       <c r="H54" t="n">
-        <v>3139</v>
+        <v>3216</v>
       </c>
       <c r="I54" t="n">
-        <v>75976.61</v>
+        <v>79812.84</v>
       </c>
       <c r="J54" t="n">
         <v>22</v>
       </c>
       <c r="K54" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L54" t="n">
         <v>25</v>
       </c>
       <c r="M54" t="n">
-        <v>5623</v>
+        <v>5799</v>
       </c>
     </row>
     <row r="55">
@@ -2946,25 +2941,25 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>2528</v>
+        <v>2594</v>
       </c>
       <c r="H55" t="n">
-        <v>3194</v>
+        <v>3277</v>
       </c>
       <c r="I55" t="n">
-        <v>79718.06</v>
+        <v>83448.23</v>
       </c>
       <c r="J55" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K55" t="n">
         <v>72</v>
       </c>
       <c r="L55" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M55" t="n">
-        <v>5129</v>
+        <v>6401</v>
       </c>
     </row>
     <row r="56">
@@ -2978,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2987,22 +2982,22 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>2369</v>
+        <v>2444</v>
       </c>
       <c r="H56" t="n">
-        <v>3029</v>
+        <v>3118</v>
       </c>
       <c r="I56" t="n">
-        <v>74258.71000000001</v>
+        <v>78260.82000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K56" t="n">
         <v>49</v>
       </c>
       <c r="L56" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M56" t="n">
         <v>5244</v>
@@ -3016,7 +3011,7 @@
         <v>3</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -3028,13 +3023,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>2421</v>
+        <v>2467</v>
       </c>
       <c r="H57" t="n">
-        <v>3090</v>
+        <v>3150</v>
       </c>
       <c r="I57" t="n">
-        <v>76564.10000000001</v>
+        <v>78531.5</v>
       </c>
       <c r="J57" t="n">
         <v>19</v>
@@ -3043,10 +3038,10 @@
         <v>69</v>
       </c>
       <c r="L57" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M57" t="n">
-        <v>6694</v>
+        <v>5621</v>
       </c>
     </row>
     <row r="58">
@@ -3054,7 +3049,7 @@
         <v>46260</v>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -3069,13 +3064,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>2581</v>
+        <v>2669</v>
       </c>
       <c r="H58" t="n">
-        <v>3286</v>
+        <v>3389</v>
       </c>
       <c r="I58" t="n">
-        <v>81185.14</v>
+        <v>85854.11</v>
       </c>
       <c r="J58" t="n">
         <v>22</v>
@@ -3087,7 +3082,7 @@
         <v>22</v>
       </c>
       <c r="M58" t="n">
-        <v>5352</v>
+        <v>6683</v>
       </c>
     </row>
     <row r="59">
@@ -3110,16 +3105,16 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>2507</v>
+        <v>2566</v>
       </c>
       <c r="H59" t="n">
-        <v>3242</v>
+        <v>3315</v>
       </c>
       <c r="I59" t="n">
-        <v>80249.58</v>
+        <v>82484.85000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K59" t="n">
         <v>74</v>
@@ -3128,7 +3123,7 @@
         <v>17</v>
       </c>
       <c r="M59" t="n">
-        <v>5019</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="60">
@@ -3151,13 +3146,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>2514</v>
+        <v>2598</v>
       </c>
       <c r="H60" t="n">
-        <v>3193</v>
+        <v>3295</v>
       </c>
       <c r="I60" t="n">
-        <v>80665.07000000001</v>
+        <v>84546.05</v>
       </c>
       <c r="J60" t="n">
         <v>24</v>
@@ -3166,7 +3161,7 @@
         <v>59</v>
       </c>
       <c r="L60" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M60" t="n">
         <v>4929</v>
@@ -3177,7 +3172,7 @@
         <v>46263</v>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -3192,13 +3187,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>2618</v>
+        <v>2685</v>
       </c>
       <c r="H61" t="n">
-        <v>3383</v>
+        <v>3471</v>
       </c>
       <c r="I61" t="n">
-        <v>81709.17</v>
+        <v>84395.28999999999</v>
       </c>
       <c r="J61" t="n">
         <v>20</v>
@@ -3207,7 +3202,7 @@
         <v>62</v>
       </c>
       <c r="L61" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M61" t="n">
         <v>4492</v>
@@ -3224,7 +3219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E332"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7967,16 +7962,16 @@
     </row>
     <row r="226">
       <c r="A226" s="3" t="n">
-        <v>46243.68306712963</v>
+        <v>46243.76186342593</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>PET-99222</t>
+          <t>HEA-72981</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -7988,16 +7983,16 @@
     </row>
     <row r="227">
       <c r="A227" s="3" t="n">
-        <v>46243.70954861111</v>
+        <v>46243.85148148148</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>PET-99222</t>
+          <t>HOM-64386</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8009,16 +8004,16 @@
     </row>
     <row r="228">
       <c r="A228" s="3" t="n">
-        <v>46243.7440162037</v>
+        <v>46244.75303240741</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>PET-99222</t>
+          <t>APP-48521</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8030,16 +8025,16 @@
     </row>
     <row r="229">
       <c r="A229" s="3" t="n">
-        <v>46243.75071759259</v>
+        <v>46244.95229166667</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>PET-99222</t>
+          <t>SPO-73706</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8051,7 +8046,7 @@
     </row>
     <row r="230">
       <c r="A230" s="3" t="n">
-        <v>46243.76186342593</v>
+        <v>46245.46832175926</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -8060,7 +8055,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>HEA-72981</t>
+          <t>HOM-69075</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8072,7 +8067,7 @@
     </row>
     <row r="231">
       <c r="A231" s="3" t="n">
-        <v>46243.80307870371</v>
+        <v>46245.8706712963</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -8081,7 +8076,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>PET-99222</t>
+          <t>HOM-69075</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8093,16 +8088,16 @@
     </row>
     <row r="232">
       <c r="A232" s="3" t="n">
-        <v>46243.81855324074</v>
+        <v>46246.6356712963</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>PET-99222</t>
+          <t>TEC-44842</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8114,7 +8109,7 @@
     </row>
     <row r="233">
       <c r="A233" s="3" t="n">
-        <v>46243.84143518518</v>
+        <v>46246.66284722222</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -8123,7 +8118,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>PET-99222</t>
+          <t>HOM-61349</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8135,16 +8130,16 @@
     </row>
     <row r="234">
       <c r="A234" s="3" t="n">
-        <v>46243.84552083333</v>
+        <v>46246.80615740741</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>PET-99222</t>
+          <t>HOM-61349</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8156,28 +8151,28 @@
     </row>
     <row r="235">
       <c r="A235" s="3" t="n">
-        <v>46243.85148148148</v>
+        <v>46246.85045138889</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>HOM-64386</t>
+          <t>PET-82682</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="n">
-        <v>46243.86778935185</v>
+        <v>46246.8903125</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -8186,7 +8181,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>PET-99222</t>
+          <t>APP-47734</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8198,28 +8193,28 @@
     </row>
     <row r="237">
       <c r="A237" s="3" t="n">
-        <v>46244.65722222222</v>
+        <v>46248.63248842592</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>SPO-98603</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="n">
-        <v>46244.66483796296</v>
+        <v>46249.6427662037</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -8228,19 +8223,19 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>TOY-18677</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="3" t="n">
-        <v>46244.70577546296</v>
+        <v>46251.88578703703</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -8249,7 +8244,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>HOM-51348</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8261,16 +8256,16 @@
     </row>
     <row r="240">
       <c r="A240" s="3" t="n">
-        <v>46244.71332175926</v>
+        <v>46252.56491898148</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>TEC-46743</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8282,7 +8277,7 @@
     </row>
     <row r="241">
       <c r="A241" s="3" t="n">
-        <v>46244.73041666667</v>
+        <v>46252.78939814815</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -8291,11 +8286,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>PET-13410</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E241" t="n">
         <v>0</v>
@@ -8303,7 +8298,7 @@
     </row>
     <row r="242">
       <c r="A242" s="3" t="n">
-        <v>46244.73652777778</v>
+        <v>46253.84681712963</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -8312,11 +8307,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>BEA-91613</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E242" t="n">
         <v>0</v>
@@ -8324,7 +8319,7 @@
     </row>
     <row r="243">
       <c r="A243" s="3" t="n">
-        <v>46244.73740740741</v>
+        <v>46253.89300925926</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -8333,19 +8328,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>BEA-43568</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="n">
-        <v>46244.74313657408</v>
+        <v>46253.9346412037</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -8354,7 +8349,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>GAR-21599</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8366,16 +8361,16 @@
     </row>
     <row r="245">
       <c r="A245" s="3" t="n">
-        <v>46244.74553240741</v>
+        <v>46255.82412037037</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>TEC-85246</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -8387,16 +8382,16 @@
     </row>
     <row r="246">
       <c r="A246" s="3" t="n">
-        <v>46244.74618055556</v>
+        <v>46255.8483449074</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>TEC-85246</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -8408,16 +8403,16 @@
     </row>
     <row r="247">
       <c r="A247" s="3" t="n">
-        <v>46244.75297453703</v>
+        <v>46257.70395833333</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>BEA-90677</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -8429,16 +8424,16 @@
     </row>
     <row r="248">
       <c r="A248" s="3" t="n">
-        <v>46244.75303240741</v>
+        <v>46257.96581018518</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>APP-48521</t>
+          <t>SPO-11580</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -8450,7 +8445,7 @@
     </row>
     <row r="249">
       <c r="A249" s="3" t="n">
-        <v>46244.75706018518</v>
+        <v>46257.99844907408</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -8459,7 +8454,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>SPO-11580</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -8471,16 +8466,16 @@
     </row>
     <row r="250">
       <c r="A250" s="3" t="n">
-        <v>46244.76528935185</v>
+        <v>46258.64458333333</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>PET-90822</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -8492,28 +8487,28 @@
     </row>
     <row r="251">
       <c r="A251" s="3" t="n">
-        <v>46244.76881944444</v>
+        <v>46258.71694444444</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>SPO-76571</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="3" t="n">
-        <v>46244.77165509259</v>
+        <v>46259.62512731482</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -8522,19 +8517,19 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>APP-66231</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="3" t="n">
-        <v>46244.80370370371</v>
+        <v>46259.83806712963</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -8543,19 +8538,19 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>BEA-73004</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="3" t="n">
-        <v>46244.8044212963</v>
+        <v>46259.96693287037</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -8564,7 +8559,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>TOY-88371</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -8576,7 +8571,7 @@
     </row>
     <row r="255">
       <c r="A255" s="3" t="n">
-        <v>46244.82546296297</v>
+        <v>46261.64368055556</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -8585,7 +8580,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>HOM-30879</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -8597,20 +8592,20 @@
     </row>
     <row r="256">
       <c r="A256" s="3" t="n">
-        <v>46244.83798611111</v>
+        <v>46261.95210648148</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>HOM-30879</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E256" t="n">
         <v>0</v>
@@ -8618,7 +8613,7 @@
     </row>
     <row r="257">
       <c r="A257" s="3" t="n">
-        <v>46244.84209490741</v>
+        <v>46262.55337962963</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -8627,7 +8622,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>HOM-49381</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -8639,1577 +8634,23 @@
     </row>
     <row r="258">
       <c r="A258" s="3" t="n">
-        <v>46244.8700462963</v>
+        <v>46263.5819212963</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>HOM-34353</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E258" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="3" t="n">
-        <v>46244.87329861111</v>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>PET-38965</t>
-        </is>
-      </c>
-      <c r="D259" t="n">
-        <v>1</v>
-      </c>
-      <c r="E259" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="3" t="n">
-        <v>46244.88443287037</v>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>PET-38965</t>
-        </is>
-      </c>
-      <c r="D260" t="n">
-        <v>1</v>
-      </c>
-      <c r="E260" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="3" t="n">
-        <v>46244.88480324074</v>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>PET-38965</t>
-        </is>
-      </c>
-      <c r="D261" t="n">
-        <v>1</v>
-      </c>
-      <c r="E261" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="3" t="n">
-        <v>46244.895625</v>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>PET-38965</t>
-        </is>
-      </c>
-      <c r="D262" t="n">
-        <v>1</v>
-      </c>
-      <c r="E262" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="3" t="n">
-        <v>46244.95229166667</v>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>SPO-73706</t>
-        </is>
-      </c>
-      <c r="D263" t="n">
-        <v>1</v>
-      </c>
-      <c r="E263" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="3" t="n">
-        <v>46245.46832175926</v>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>HOM-69075</t>
-        </is>
-      </c>
-      <c r="D264" t="n">
-        <v>1</v>
-      </c>
-      <c r="E264" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="3" t="n">
-        <v>46245.8706712963</v>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>HOM-69075</t>
-        </is>
-      </c>
-      <c r="D265" t="n">
-        <v>1</v>
-      </c>
-      <c r="E265" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="3" t="n">
-        <v>46246.16149305556</v>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>PET-38965</t>
-        </is>
-      </c>
-      <c r="D266" t="n">
-        <v>1</v>
-      </c>
-      <c r="E266" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="3" t="n">
-        <v>46246.23771990741</v>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>PET-38965</t>
-        </is>
-      </c>
-      <c r="D267" t="n">
-        <v>2</v>
-      </c>
-      <c r="E267" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="3" t="n">
-        <v>46246.25157407407</v>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>PET-38965</t>
-        </is>
-      </c>
-      <c r="D268" t="n">
-        <v>1</v>
-      </c>
-      <c r="E268" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="3" t="n">
-        <v>46246.26868055556</v>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>PET-38965</t>
-        </is>
-      </c>
-      <c r="D269" t="n">
-        <v>1</v>
-      </c>
-      <c r="E269" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="3" t="n">
-        <v>46246.29255787037</v>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>PET-38965</t>
-        </is>
-      </c>
-      <c r="D270" t="n">
-        <v>1</v>
-      </c>
-      <c r="E270" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="3" t="n">
-        <v>46246.35886574074</v>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>PET-38965</t>
-        </is>
-      </c>
-      <c r="D271" t="n">
-        <v>1</v>
-      </c>
-      <c r="E271" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="3" t="n">
-        <v>46246.403125</v>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>PET-38965</t>
-        </is>
-      </c>
-      <c r="D272" t="n">
-        <v>1</v>
-      </c>
-      <c r="E272" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="3" t="n">
-        <v>46246.6356712963</v>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>TEC-44842</t>
-        </is>
-      </c>
-      <c r="D273" t="n">
-        <v>1</v>
-      </c>
-      <c r="E273" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="3" t="n">
-        <v>46246.66284722222</v>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>HOM-61349</t>
-        </is>
-      </c>
-      <c r="D274" t="n">
-        <v>1</v>
-      </c>
-      <c r="E274" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="3" t="n">
-        <v>46246.80615740741</v>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>HOM-61349</t>
-        </is>
-      </c>
-      <c r="D275" t="n">
-        <v>1</v>
-      </c>
-      <c r="E275" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="3" t="n">
-        <v>46246.85045138889</v>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>PET-82682</t>
-        </is>
-      </c>
-      <c r="D276" t="n">
-        <v>3</v>
-      </c>
-      <c r="E276" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="3" t="n">
-        <v>46246.8903125</v>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>APP-47734</t>
-        </is>
-      </c>
-      <c r="D277" t="n">
-        <v>1</v>
-      </c>
-      <c r="E277" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="3" t="n">
-        <v>46247.03377314815</v>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>PET-38965</t>
-        </is>
-      </c>
-      <c r="D278" t="n">
-        <v>1</v>
-      </c>
-      <c r="E278" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="3" t="n">
-        <v>46248.63248842592</v>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>SPO-98603</t>
-        </is>
-      </c>
-      <c r="D279" t="n">
-        <v>2</v>
-      </c>
-      <c r="E279" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="3" t="n">
-        <v>46248.93430555556</v>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>PET-99222</t>
-        </is>
-      </c>
-      <c r="D280" t="n">
-        <v>1</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="3" t="n">
-        <v>46249.6427662037</v>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>TOY-18677</t>
-        </is>
-      </c>
-      <c r="D281" t="n">
-        <v>2</v>
-      </c>
-      <c r="E281" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="3" t="n">
-        <v>46250.91362268518</v>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>TOY-74255</t>
-        </is>
-      </c>
-      <c r="D282" t="n">
-        <v>1</v>
-      </c>
-      <c r="E282" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="3" t="n">
-        <v>46250.99244212963</v>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>TOY-74255</t>
-        </is>
-      </c>
-      <c r="D283" t="n">
-        <v>3</v>
-      </c>
-      <c r="E283" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="3" t="n">
-        <v>46251.80489583333</v>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>APP-18249</t>
-        </is>
-      </c>
-      <c r="D284" t="n">
-        <v>2</v>
-      </c>
-      <c r="E284" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="3" t="n">
-        <v>46251.81123842593</v>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>APP-18249</t>
-        </is>
-      </c>
-      <c r="D285" t="n">
-        <v>2</v>
-      </c>
-      <c r="E285" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="3" t="n">
-        <v>46251.83168981481</v>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>APP-18249</t>
-        </is>
-      </c>
-      <c r="D286" t="n">
-        <v>2</v>
-      </c>
-      <c r="E286" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="3" t="n">
-        <v>46251.8746875</v>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>APP-18249</t>
-        </is>
-      </c>
-      <c r="D287" t="n">
-        <v>1</v>
-      </c>
-      <c r="E287" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="3" t="n">
-        <v>46251.87559027778</v>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>APP-18249</t>
-        </is>
-      </c>
-      <c r="D288" t="n">
-        <v>1</v>
-      </c>
-      <c r="E288" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="3" t="n">
-        <v>46251.88578703703</v>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>HOM-51348</t>
-        </is>
-      </c>
-      <c r="D289" t="n">
-        <v>1</v>
-      </c>
-      <c r="E289" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="3" t="n">
-        <v>46251.91256944444</v>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>APP-18249</t>
-        </is>
-      </c>
-      <c r="D290" t="n">
-        <v>1</v>
-      </c>
-      <c r="E290" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="3" t="n">
-        <v>46251.9608912037</v>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>APP-18249</t>
-        </is>
-      </c>
-      <c r="D291" t="n">
-        <v>1</v>
-      </c>
-      <c r="E291" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="3" t="n">
-        <v>46251.96729166667</v>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>APP-18249</t>
-        </is>
-      </c>
-      <c r="D292" t="n">
-        <v>1</v>
-      </c>
-      <c r="E292" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="3" t="n">
-        <v>46251.98641203704</v>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>APP-18249</t>
-        </is>
-      </c>
-      <c r="D293" t="n">
-        <v>1</v>
-      </c>
-      <c r="E293" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="3" t="n">
-        <v>46252.56491898148</v>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>TEC-46743</t>
-        </is>
-      </c>
-      <c r="D294" t="n">
-        <v>1</v>
-      </c>
-      <c r="E294" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="3" t="n">
-        <v>46252.78939814815</v>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>PET-13410</t>
-        </is>
-      </c>
-      <c r="D295" t="n">
-        <v>1</v>
-      </c>
-      <c r="E295" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="3" t="n">
-        <v>46253.84681712963</v>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>BEA-91613</t>
-        </is>
-      </c>
-      <c r="D296" t="n">
-        <v>1</v>
-      </c>
-      <c r="E296" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="3" t="n">
-        <v>46253.89300925926</v>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>BEA-43568</t>
-        </is>
-      </c>
-      <c r="D297" t="n">
-        <v>3</v>
-      </c>
-      <c r="E297" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="3" t="n">
-        <v>46253.9346412037</v>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>GAR-21599</t>
-        </is>
-      </c>
-      <c r="D298" t="n">
-        <v>1</v>
-      </c>
-      <c r="E298" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="3" t="n">
-        <v>46255.6265162037</v>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>SPO-36472</t>
-        </is>
-      </c>
-      <c r="D299" t="n">
-        <v>1</v>
-      </c>
-      <c r="E299" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="3" t="n">
-        <v>46255.69508101852</v>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>SPO-36472</t>
-        </is>
-      </c>
-      <c r="D300" t="n">
-        <v>1</v>
-      </c>
-      <c r="E300" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="3" t="n">
-        <v>46255.75731481481</v>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>SPO-36472</t>
-        </is>
-      </c>
-      <c r="D301" t="n">
-        <v>1</v>
-      </c>
-      <c r="E301" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="3" t="n">
-        <v>46255.82412037037</v>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>TEC-85246</t>
-        </is>
-      </c>
-      <c r="D302" t="n">
-        <v>1</v>
-      </c>
-      <c r="E302" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="3" t="n">
-        <v>46255.8483449074</v>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>TEC-85246</t>
-        </is>
-      </c>
-      <c r="D303" t="n">
-        <v>1</v>
-      </c>
-      <c r="E303" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="3" t="n">
-        <v>46255.94096064815</v>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>SPO-36472</t>
-        </is>
-      </c>
-      <c r="D304" t="n">
-        <v>1</v>
-      </c>
-      <c r="E304" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="3" t="n">
-        <v>46256.81952546296</v>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D305" t="n">
-        <v>1</v>
-      </c>
-      <c r="E305" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="3" t="n">
-        <v>46256.82460648148</v>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D306" t="n">
-        <v>1</v>
-      </c>
-      <c r="E306" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="3" t="n">
-        <v>46256.82512731481</v>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D307" t="n">
-        <v>1</v>
-      </c>
-      <c r="E307" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="3" t="n">
-        <v>46256.83739583333</v>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D308" t="n">
-        <v>1</v>
-      </c>
-      <c r="E308" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="3" t="n">
-        <v>46256.84755787037</v>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D309" t="n">
-        <v>1</v>
-      </c>
-      <c r="E309" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="3" t="n">
-        <v>46256.85371527778</v>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D310" t="n">
-        <v>1</v>
-      </c>
-      <c r="E310" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="3" t="n">
-        <v>46256.87375</v>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D311" t="n">
-        <v>1</v>
-      </c>
-      <c r="E311" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="3" t="n">
-        <v>46256.88517361111</v>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D312" t="n">
-        <v>2</v>
-      </c>
-      <c r="E312" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="3" t="n">
-        <v>46256.90975694444</v>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D313" t="n">
-        <v>1</v>
-      </c>
-      <c r="E313" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="3" t="n">
-        <v>46256.97103009259</v>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D314" t="n">
-        <v>1</v>
-      </c>
-      <c r="E314" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="3" t="n">
-        <v>46257.70395833333</v>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>BEA-90677</t>
-        </is>
-      </c>
-      <c r="D315" t="n">
-        <v>1</v>
-      </c>
-      <c r="E315" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="3" t="n">
-        <v>46257.96581018518</v>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>SPO-11580</t>
-        </is>
-      </c>
-      <c r="D316" t="n">
-        <v>1</v>
-      </c>
-      <c r="E316" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="3" t="n">
-        <v>46257.99844907408</v>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>SPO-11580</t>
-        </is>
-      </c>
-      <c r="D317" t="n">
-        <v>1</v>
-      </c>
-      <c r="E317" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="3" t="n">
-        <v>46258.64458333333</v>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>PET-90822</t>
-        </is>
-      </c>
-      <c r="D318" t="n">
-        <v>1</v>
-      </c>
-      <c r="E318" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="3" t="n">
-        <v>46258.71694444444</v>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>SPO-76571</t>
-        </is>
-      </c>
-      <c r="D319" t="n">
-        <v>2</v>
-      </c>
-      <c r="E319" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="3" t="n">
-        <v>46259.62512731482</v>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>APP-66231</t>
-        </is>
-      </c>
-      <c r="D320" t="n">
-        <v>3</v>
-      </c>
-      <c r="E320" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="3" t="n">
-        <v>46259.83806712963</v>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>BEA-73004</t>
-        </is>
-      </c>
-      <c r="D321" t="n">
-        <v>2</v>
-      </c>
-      <c r="E321" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="3" t="n">
-        <v>46259.96693287037</v>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>TOY-88371</t>
-        </is>
-      </c>
-      <c r="D322" t="n">
-        <v>1</v>
-      </c>
-      <c r="E322" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="3" t="n">
-        <v>46260.39381944444</v>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D323" t="n">
-        <v>1</v>
-      </c>
-      <c r="E323" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="3" t="n">
-        <v>46260.74949074074</v>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>TEC-84381</t>
-        </is>
-      </c>
-      <c r="D324" t="n">
-        <v>1</v>
-      </c>
-      <c r="E324" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="3" t="n">
-        <v>46260.85635416667</v>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D325" t="n">
-        <v>1</v>
-      </c>
-      <c r="E325" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="3" t="n">
-        <v>46261.64368055556</v>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>HOM-30879</t>
-        </is>
-      </c>
-      <c r="D326" t="n">
-        <v>1</v>
-      </c>
-      <c r="E326" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="3" t="n">
-        <v>46261.95210648148</v>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>HOM-30879</t>
-        </is>
-      </c>
-      <c r="D327" t="n">
-        <v>1</v>
-      </c>
-      <c r="E327" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="3" t="n">
-        <v>46262.55337962963</v>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>HOM-49381</t>
-        </is>
-      </c>
-      <c r="D328" t="n">
-        <v>1</v>
-      </c>
-      <c r="E328" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="3" t="n">
-        <v>46263.48149305556</v>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D329" t="n">
-        <v>1</v>
-      </c>
-      <c r="E329" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="3" t="n">
-        <v>46263.51401620371</v>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>TEC-52001</t>
-        </is>
-      </c>
-      <c r="D330" t="n">
-        <v>1</v>
-      </c>
-      <c r="E330" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="3" t="n">
-        <v>46263.5819212963</v>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>HOM-34353</t>
-        </is>
-      </c>
-      <c r="D331" t="n">
-        <v>2</v>
-      </c>
-      <c r="E331" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="3" t="n">
-        <v>46263.68962962963</v>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>OFF-30854</t>
-        </is>
-      </c>
-      <c r="D332" t="n">
-        <v>2</v>
-      </c>
-      <c r="E332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/out/07_Before_vs_After.xlsx
+++ b/out/07_Before_vs_After.xlsx
@@ -667,11 +667,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -689,27 +689,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>oversold orders - sync 1440m</t>
+          <t>oversold: daily sync</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>oversold orders - sync 240m</t>
+          <t>oversold: 4-hour sync</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>oversold orders - sync 60m</t>
+          <t>oversold: hourly sync</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>oversold orders - sync 15m</t>
+          <t>oversold: 15-min sync</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>oversold orders - engine</t>
+          <t>oversold: engine</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/out/07_Before_vs_After.xlsx
+++ b/out/07_Before_vs_After.xlsx
@@ -426,18 +426,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,25 +462,20 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>phantom-locked units</t>
+          <t>units sold</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>units sold</t>
+          <t>revenue USD</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>revenue USD</t>
+          <t>cancel cost USD (low)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>cancel cost USD (low)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>cancel cost USD (high)</t>
         </is>
@@ -499,25 +493,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="D2" t="n">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="E2" t="n">
-        <v>1144</v>
+        <v>193797</v>
       </c>
       <c r="F2" t="n">
-        <v>193641</v>
+        <v>4870282.03</v>
       </c>
       <c r="G2" t="n">
-        <v>4866058.59</v>
+        <v>9983</v>
       </c>
       <c r="H2" t="n">
-        <v>10735</v>
-      </c>
-      <c r="I2" t="n">
-        <v>27147</v>
+        <v>25246</v>
       </c>
     </row>
     <row r="3">
@@ -532,25 +523,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E3" t="n">
-        <v>1147</v>
+        <v>194442</v>
       </c>
       <c r="F3" t="n">
-        <v>194296</v>
+        <v>4888488.58</v>
       </c>
       <c r="G3" t="n">
-        <v>4884558.04</v>
+        <v>2548</v>
       </c>
       <c r="H3" t="n">
-        <v>2339</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5915</v>
+        <v>6443</v>
       </c>
     </row>
     <row r="4">
@@ -565,25 +553,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>1147</v>
+        <v>194457</v>
       </c>
       <c r="F4" t="n">
-        <v>194310</v>
+        <v>4888829.43</v>
       </c>
       <c r="G4" t="n">
-        <v>4884870.9</v>
+        <v>710</v>
       </c>
       <c r="H4" t="n">
-        <v>585</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1479</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="5">
@@ -604,18 +589,15 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>1147</v>
+        <v>194460</v>
       </c>
       <c r="F5" t="n">
-        <v>194313</v>
+        <v>4888905.4</v>
       </c>
       <c r="G5" t="n">
-        <v>4884946.87</v>
+        <v>334</v>
       </c>
       <c r="H5" t="n">
-        <v>334</v>
-      </c>
-      <c r="I5" t="n">
         <v>845</v>
       </c>
     </row>
@@ -637,19 +619,46 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>194459</v>
       </c>
       <c r="F6" t="n">
-        <v>194447</v>
+        <v>4888885.41</v>
       </c>
       <c r="G6" t="n">
-        <v>4888451.53</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>This engine, stress test</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pushes 20x slower</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>194459</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4888890.41</v>
+      </c>
+      <c r="G7" t="n">
+        <v>167</v>
+      </c>
+      <c r="H7" t="n">
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -903,7 +912,7 @@
         <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L5" t="n">
         <v>5</v>
@@ -1040,7 +1049,7 @@
         <v>46211</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -1122,10 +1131,10 @@
         <v>46213</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -1137,13 +1146,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="H11" t="n">
-        <v>3280</v>
+        <v>3281</v>
       </c>
       <c r="I11" t="n">
-        <v>84845.2</v>
+        <v>84881.19</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
@@ -1152,7 +1161,7 @@
         <v>178</v>
       </c>
       <c r="L11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M11" t="n">
         <v>2663</v>
@@ -1163,37 +1172,37 @@
         <v>46214</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="H12" t="n">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="I12" t="n">
-        <v>79419</v>
+        <v>79442.99000000001</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M12" t="n">
         <v>2411</v>
@@ -1204,10 +1213,10 @@
         <v>46215</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -1292,10 +1301,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1395,7 +1404,7 @@
         <v>24</v>
       </c>
       <c r="K17" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L17" t="n">
         <v>22</v>
@@ -1450,7 +1459,7 @@
         <v>46221</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1491,7 +1500,7 @@
         <v>46222</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1532,14 +1541,14 @@
         <v>46223</v>
       </c>
       <c r="B21" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="n">
         <v>3</v>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
@@ -1547,19 +1556,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="H21" t="n">
-        <v>3244</v>
+        <v>3245</v>
       </c>
       <c r="I21" t="n">
-        <v>81302.56</v>
+        <v>81336.55</v>
       </c>
       <c r="J21" t="n">
         <v>23</v>
       </c>
       <c r="K21" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L21" t="n">
         <v>45</v>
@@ -1588,13 +1597,13 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="H22" t="n">
-        <v>3203</v>
+        <v>3205</v>
       </c>
       <c r="I22" t="n">
-        <v>79447.97</v>
+        <v>79479.95</v>
       </c>
       <c r="J22" t="n">
         <v>24</v>
@@ -1603,7 +1612,7 @@
         <v>169</v>
       </c>
       <c r="L22" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M22" t="n">
         <v>2958</v>
@@ -1614,7 +1623,7 @@
         <v>46225</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
         <v>7</v>
@@ -1655,7 +1664,7 @@
         <v>46226</v>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
@@ -1670,13 +1679,13 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="H24" t="n">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="I24" t="n">
-        <v>81156</v>
+        <v>81173.99000000001</v>
       </c>
       <c r="J24" t="n">
         <v>24</v>
@@ -1726,7 +1735,7 @@
         <v>180</v>
       </c>
       <c r="L25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M25" t="n">
         <v>6264</v>
@@ -1752,19 +1761,19 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="H26" t="n">
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="I26" t="n">
-        <v>75609.2</v>
+        <v>75669.19</v>
       </c>
       <c r="J26" t="n">
         <v>24</v>
       </c>
       <c r="K26" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L26" t="n">
         <v>51</v>
@@ -1778,7 +1787,7 @@
         <v>46229</v>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
         <v>3</v>
@@ -1793,13 +1802,13 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="H27" t="n">
-        <v>3223</v>
+        <v>3224</v>
       </c>
       <c r="I27" t="n">
-        <v>80229.77</v>
+        <v>80248.75999999999</v>
       </c>
       <c r="J27" t="n">
         <v>24</v>
@@ -1808,7 +1817,7 @@
         <v>137</v>
       </c>
       <c r="L27" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M27" t="n">
         <v>6892</v>
@@ -1819,7 +1828,7 @@
         <v>46230</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1834,19 +1843,19 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="H28" t="n">
-        <v>3014</v>
+        <v>3016</v>
       </c>
       <c r="I28" t="n">
-        <v>75652.86</v>
+        <v>75822.84</v>
       </c>
       <c r="J28" t="n">
         <v>23</v>
       </c>
       <c r="K28" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L28" t="n">
         <v>60</v>
@@ -1860,7 +1869,7 @@
         <v>46231</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
         <v>3</v>
@@ -1901,13 +1910,13 @@
         <v>46232</v>
       </c>
       <c r="B30" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -1916,13 +1925,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="H30" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="I30" t="n">
-        <v>77100.39999999999</v>
+        <v>77155.39</v>
       </c>
       <c r="J30" t="n">
         <v>24</v>
@@ -1983,10 +1992,10 @@
         <v>46234</v>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -2001,10 +2010,10 @@
         <v>2531</v>
       </c>
       <c r="H32" t="n">
-        <v>3220</v>
+        <v>3221</v>
       </c>
       <c r="I32" t="n">
-        <v>80603.8</v>
+        <v>80645.78999999999</v>
       </c>
       <c r="J32" t="n">
         <v>24</v>
@@ -2065,7 +2074,7 @@
         <v>46236</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -2106,7 +2115,7 @@
         <v>46237</v>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
         <v>2</v>
@@ -2133,7 +2142,7 @@
         <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L35" t="n">
         <v>34</v>
@@ -2215,7 +2224,7 @@
         <v>24</v>
       </c>
       <c r="K37" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L37" t="n">
         <v>31</v>
@@ -2270,10 +2279,10 @@
         <v>46241</v>
       </c>
       <c r="B39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2300,7 +2309,7 @@
         <v>121</v>
       </c>
       <c r="L39" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M39" t="n">
         <v>9388</v>
@@ -2326,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>2774</v>
+        <v>2775</v>
       </c>
       <c r="H40" t="n">
-        <v>3591</v>
+        <v>3592</v>
       </c>
       <c r="I40" t="n">
-        <v>91036.09</v>
+        <v>91063.08</v>
       </c>
       <c r="J40" t="n">
         <v>24</v>
@@ -2341,7 +2350,7 @@
         <v>109</v>
       </c>
       <c r="L40" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M40" t="n">
         <v>10181</v>
@@ -2420,7 +2429,7 @@
         <v>23</v>
       </c>
       <c r="K42" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L42" t="n">
         <v>32</v>
@@ -2434,10 +2443,10 @@
         <v>46245</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2666,7 +2675,7 @@
         <v>23</v>
       </c>
       <c r="K48" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L48" t="n">
         <v>21</v>
@@ -2762,7 +2771,7 @@
         <v>46253</v>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -2900,13 +2909,13 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="H54" t="n">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="I54" t="n">
-        <v>79812.84</v>
+        <v>79792.85000000001</v>
       </c>
       <c r="J54" t="n">
         <v>22</v>
@@ -2926,7 +2935,7 @@
         <v>46257</v>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -2956,7 +2965,7 @@
         <v>72</v>
       </c>
       <c r="L55" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M55" t="n">
         <v>6401</v>
@@ -2994,7 +3003,7 @@
         <v>23</v>
       </c>
       <c r="K56" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L56" t="n">
         <v>7</v>
@@ -3008,10 +3017,10 @@
         <v>46259</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -3023,13 +3032,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="H57" t="n">
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="I57" t="n">
-        <v>78531.5</v>
+        <v>78553.49000000001</v>
       </c>
       <c r="J57" t="n">
         <v>19</v>
@@ -3076,7 +3085,7 @@
         <v>22</v>
       </c>
       <c r="K58" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L58" t="n">
         <v>22</v>
@@ -3090,10 +3099,10 @@
         <v>46261</v>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -3131,10 +3140,10 @@
         <v>46262</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -3161,7 +3170,7 @@
         <v>59</v>
       </c>
       <c r="L60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M60" t="n">
         <v>4929</v>
@@ -3172,7 +3181,7 @@
         <v>46263</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -3187,13 +3196,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="H61" t="n">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="I61" t="n">
-        <v>84395.28999999999</v>
+        <v>84310.3</v>
       </c>
       <c r="J61" t="n">
         <v>20</v>
@@ -3219,7 +3228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E258"/>
+  <dimension ref="A1:E240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3531,7 +3540,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46211.89878472222</v>
+        <v>46211.8874074074</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3540,7 +3549,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SPO-26749</t>
+          <t>TEC-21288</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -3552,7 +3561,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46211.9958912037</v>
+        <v>46211.89878472222</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3561,7 +3570,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OFF-62279</t>
+          <t>SPO-26749</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -3573,16 +3582,16 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46212.3712037037</v>
+        <v>46211.9958912037</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SPO-73654</t>
+          <t>OFF-62279</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -3594,16 +3603,16 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46212.44863425926</v>
+        <v>46212.3712037037</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TOY-15153</t>
+          <t>SPO-73654</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3615,16 +3624,16 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46212.930625</v>
+        <v>46212.44863425926</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HOM-62156</t>
+          <t>TOY-15153</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -3636,16 +3645,16 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46213.36299768519</v>
+        <v>46212.930625</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TEC-70865</t>
+          <t>HOM-62156</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3657,7 +3666,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46213.39329861111</v>
+        <v>46213.36299768519</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3666,7 +3675,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SPO-57977</t>
+          <t>TEC-70865</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3678,16 +3687,16 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46213.42402777778</v>
+        <v>46213.39329861111</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SPO-13416</t>
+          <t>SPO-57977</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3699,7 +3708,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46213.45186342593</v>
+        <v>46213.45824074074</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3720,11 +3729,11 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46213.45824074074</v>
+        <v>46213.48863425926</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3741,11 +3750,11 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46213.48863425926</v>
+        <v>46213.5036574074</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3762,11 +3771,11 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46213.5036574074</v>
+        <v>46213.52173611111</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3783,11 +3792,11 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46213.52173611111</v>
+        <v>46213.54842592592</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3804,11 +3813,11 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46213.54842592592</v>
+        <v>46213.5739699074</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3825,7 +3834,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46213.5739699074</v>
+        <v>46213.57756944445</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3846,7 +3855,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46213.57756944445</v>
+        <v>46213.58584490741</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3867,11 +3876,11 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46213.58584490741</v>
+        <v>46213.60548611111</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4161,20 +4170,20 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46213.92342592592</v>
+        <v>46213.89</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BEA-43249</t>
+          <t>SPO-13416</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -4203,16 +4212,16 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46214.75959490741</v>
+        <v>46214.86849537037</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SPO-66083</t>
+          <t>GAR-18518</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -4224,16 +4233,16 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46214.86849537037</v>
+        <v>46215.65010416666</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GAR-18518</t>
+          <t>HEA-81542</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -4371,11 +4380,11 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46217.38767361111</v>
+        <v>46217.39086805555</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4392,16 +4401,16 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46217.93917824074</v>
+        <v>46217.70384259259</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HOM-93186</t>
+          <t>TEC-85246</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -4513,7 +4522,7 @@
         <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -4644,16 +4653,16 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46221.7237962963</v>
+        <v>46221.8706712963</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PET-97251</t>
+          <t>HOM-70883</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -4665,11 +4674,11 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46221.8071412037</v>
+        <v>46221.88976851852</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4686,37 +4695,37 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46221.8706712963</v>
+        <v>46221.88998842592</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HOM-70883</t>
+          <t>BEA-92934</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46221.88976851852</v>
+        <v>46221.91271990741</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HOM-70883</t>
+          <t>HEA-76922</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -4728,16 +4737,16 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46221.88998842592</v>
+        <v>46221.92996527778</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BEA-92934</t>
+          <t>HEA-32320</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -4749,16 +4758,16 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46221.91271990741</v>
+        <v>46222.41783564815</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HEA-76922</t>
+          <t>HEA-32320</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -4770,16 +4779,16 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46221.92996527778</v>
+        <v>46222.5946412037</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HEA-32320</t>
+          <t>BEA-31206</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -4791,7 +4800,7 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46222.41783564815</v>
+        <v>46222.65725694445</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -4800,7 +4809,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HEA-32320</t>
+          <t>BEA-29364</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -4812,28 +4821,28 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46222.5946412037</v>
+        <v>46222.73680555556</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BEA-31206</t>
+          <t>HOM-91840</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46222.65725694445</v>
+        <v>46222.78543981481</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -4842,7 +4851,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BEA-29364</t>
+          <t>HOM-49381</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -4854,16 +4863,16 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46222.78543981481</v>
+        <v>46222.86675925926</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HOM-49381</t>
+          <t>PET-97251</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -4896,7 +4905,7 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46223.65299768518</v>
+        <v>46223.69508101852</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -4905,7 +4914,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>TOY-98798</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -4917,7 +4926,7 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46223.66980324074</v>
+        <v>46223.71701388889</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -4926,11 +4935,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>TOY-98798</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -4938,11 +4947,11 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46223.67940972222</v>
+        <v>46223.73521990741</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4959,11 +4968,11 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46223.69487268518</v>
+        <v>46223.74305555555</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4980,16 +4989,16 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46223.69508101852</v>
+        <v>46223.74605324074</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TOY-98798</t>
+          <t>PET-38965</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -5001,7 +5010,7 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46223.70319444445</v>
+        <v>46223.75715277778</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -5014,7 +5023,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -5022,7 +5031,7 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46223.7141087963</v>
+        <v>46223.76084490741</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -5035,7 +5044,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -5043,7 +5052,7 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46223.71701388889</v>
+        <v>46223.76131944444</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5052,11 +5061,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TOY-98798</t>
+          <t>PET-38965</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -5064,7 +5073,7 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46223.71861111111</v>
+        <v>46223.77151620371</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -5077,7 +5086,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -5085,11 +5094,11 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46223.72427083334</v>
+        <v>46223.77263888889</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5106,7 +5115,7 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46223.73521990741</v>
+        <v>46223.78484953703</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -5119,7 +5128,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -5127,16 +5136,16 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46223.74305555555</v>
+        <v>46223.83549768518</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>TOY-98798</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -5148,11 +5157,11 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46223.74605324074</v>
+        <v>46223.83929398148</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5169,11 +5178,11 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46223.75715277778</v>
+        <v>46223.85429398148</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5182,7 +5191,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -5190,7 +5199,7 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46223.76084490741</v>
+        <v>46223.86126157407</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -5199,7 +5208,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>OFF-71262</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -5211,11 +5220,11 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46223.76131944444</v>
+        <v>46223.86555555555</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5224,7 +5233,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -5232,11 +5241,11 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46223.77151620371</v>
+        <v>46223.86721064815</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5253,11 +5262,11 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46223.77263888889</v>
+        <v>46223.86744212963</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5274,11 +5283,11 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46223.78484953703</v>
+        <v>46223.8734837963</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5287,7 +5296,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -5295,7 +5304,7 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46223.83549768518</v>
+        <v>46223.8799074074</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -5316,11 +5325,11 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46223.83929398148</v>
+        <v>46223.91190972222</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5329,7 +5338,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -5337,16 +5346,16 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46223.85429398148</v>
+        <v>46223.94207175926</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>TOY-77755</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -5358,20 +5367,20 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46223.86126157407</v>
+        <v>46223.94849537037</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>OFF-71262</t>
+          <t>TOY-98798</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -5379,11 +5388,11 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46223.86555555555</v>
+        <v>46223.94981481481</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5400,16 +5409,16 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46223.86721064815</v>
+        <v>46223.95690972222</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>SPO-99305</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -5421,16 +5430,16 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46223.86744212963</v>
+        <v>46224.52451388889</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>SPO-96835</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -5442,16 +5451,16 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46223.8734837963</v>
+        <v>46224.58320601852</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>SPO-96835</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -5463,7 +5472,7 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46223.8799074074</v>
+        <v>46224.6012962963</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -5472,11 +5481,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TOY-98798</t>
+          <t>TEC-28316</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
@@ -5484,49 +5493,49 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46223.91190972222</v>
+        <v>46224.70422453704</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>HOM-16474</t>
         </is>
       </c>
       <c r="D108" t="n">
         <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46223.94207175926</v>
+        <v>46224.7138425926</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TOY-77755</t>
+          <t>SPO-96534</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46223.94849537037</v>
+        <v>46224.72495370371</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -5535,11 +5544,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TOY-98798</t>
+          <t>HOM-50081</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
@@ -5547,16 +5556,16 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46223.94981481481</v>
+        <v>46224.74127314815</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>BEA-84377</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -5568,16 +5577,16 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46223.95690972222</v>
+        <v>46224.76979166667</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SPO-99305</t>
+          <t>TEC-28316</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -5589,16 +5598,16 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46224.52451388889</v>
+        <v>46224.77</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SPO-96835</t>
+          <t>BEA-84377</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -5610,7 +5619,7 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46224.5771875</v>
+        <v>46224.79681712963</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -5631,16 +5640,16 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46224.58266203704</v>
+        <v>46224.9258449074</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BEA-84377</t>
+          <t>TOY-99585</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -5652,28 +5661,28 @@
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46224.58320601852</v>
+        <v>46224.99984953704</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SPO-96835</t>
+          <t>BEA-87790</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46224.6012962963</v>
+        <v>46225.40506944444</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -5682,19 +5691,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TEC-28316</t>
+          <t>GAR-71934</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46224.70422453704</v>
+        <v>46225.52988425926</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -5703,7 +5712,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>HOM-16474</t>
+          <t>TOY-28908</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -5715,28 +5724,28 @@
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46224.7138425926</v>
+        <v>46225.78974537037</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SPO-96534</t>
+          <t>BEA-41924</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46224.72495370371</v>
+        <v>46225.80990740741</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -5745,7 +5754,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HOM-50081</t>
+          <t>HOM-34353</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -5757,16 +5766,16 @@
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46224.75077546296</v>
+        <v>46225.90552083333</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TEC-38164</t>
+          <t>TEC-90519</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -5778,7 +5787,7 @@
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46224.79681712963</v>
+        <v>46225.90684027778</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -5787,7 +5796,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BEA-84377</t>
+          <t>TEC-63901</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -5799,7 +5808,7 @@
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46224.9258449074</v>
+        <v>46226.48961805556</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -5808,7 +5817,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TOY-99585</t>
+          <t>TEC-96407</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -5820,37 +5829,37 @@
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46224.99984953704</v>
+        <v>46226.49966435185</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BEA-87790</t>
+          <t>SPO-96534</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46225.40506944444</v>
+        <v>46226.67175925926</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>GAR-71934</t>
+          <t>TEC-63646</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -5862,37 +5871,37 @@
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46225.52988425926</v>
+        <v>46226.71327546296</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TOY-28908</t>
+          <t>TOY-80142</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46225.64907407408</v>
+        <v>46226.72446759259</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TEC-88285</t>
+          <t>TEC-63646</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -5904,7 +5913,7 @@
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46225.78974537037</v>
+        <v>46226.78241898148</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -5913,7 +5922,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BEA-41924</t>
+          <t>GAR-71934</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -5925,16 +5934,16 @@
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46225.80990740741</v>
+        <v>46226.87164351852</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>HOM-34353</t>
+          <t>PET-38965</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -5946,16 +5955,16 @@
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46225.83162037037</v>
+        <v>46226.88329861111</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SPO-61851</t>
+          <t>SPO-84470</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -5967,7 +5976,7 @@
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46225.90552083333</v>
+        <v>46226.88578703703</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -5976,7 +5985,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TEC-90519</t>
+          <t>HOM-34217</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5988,16 +5997,16 @@
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46225.90684027778</v>
+        <v>46226.89098379629</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TEC-63901</t>
+          <t>PET-38965</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -6009,20 +6018,20 @@
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46226.48961805556</v>
+        <v>46226.91931712963</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TEC-96407</t>
+          <t>TOY-73928</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -6030,16 +6039,16 @@
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46226.49966435185</v>
+        <v>46226.99800925926</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SPO-96534</t>
+          <t>TOY-73928</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -6051,28 +6060,28 @@
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46226.64160879629</v>
+        <v>46227.4558912037</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>HOM-90261</t>
+          <t>BEA-77529</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46226.67175925926</v>
+        <v>46227.64260416666</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -6081,7 +6090,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TEC-63646</t>
+          <t>PET-16184</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -6093,16 +6102,16 @@
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46226.72446759259</v>
+        <v>46227.67416666666</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TEC-63646</t>
+          <t>PET-16184</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -6114,16 +6123,16 @@
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46226.78241898148</v>
+        <v>46227.84071759259</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GAR-71934</t>
+          <t>OFF-89315</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -6135,7 +6144,7 @@
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46226.87164351852</v>
+        <v>46227.87108796297</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -6144,7 +6153,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>APP-84638</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -6156,37 +6165,37 @@
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46226.88329861111</v>
+        <v>46227.92297453704</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SPO-84470</t>
+          <t>PET-99222</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46226.88578703703</v>
+        <v>46227.92961805555</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>HOM-34217</t>
+          <t>TOY-23573</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -6198,16 +6207,16 @@
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46226.89098379629</v>
+        <v>46228.13982638889</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PET-38965</t>
+          <t>PET-99222</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -6219,16 +6228,16 @@
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46226.90662037037</v>
+        <v>46228.18297453703</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>TOY-73928</t>
+          <t>PET-99222</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -6240,28 +6249,28 @@
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46227.4558912037</v>
+        <v>46228.50690972222</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BEA-77529</t>
+          <t>HEA-64165</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46227.64260416666</v>
+        <v>46228.58369212963</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -6270,7 +6279,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PET-16184</t>
+          <t>BEA-48693</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -6282,7 +6291,7 @@
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46227.67416666666</v>
+        <v>46228.59902777777</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -6291,28 +6300,28 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PET-16184</t>
+          <t>HOM-31415</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46227.84071759259</v>
+        <v>46228.65982638889</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>OFF-89315</t>
+          <t>APP-77442</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -6324,58 +6333,58 @@
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46227.87108796297</v>
+        <v>46228.83222222222</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>APP-84638</t>
+          <t>HOM-92315</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46227.92297453704</v>
+        <v>46228.83768518519</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PET-99222</t>
+          <t>PET-63231</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46227.92961805555</v>
+        <v>46229.3334375</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TOY-23573</t>
+          <t>TOY-31935</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -6387,7 +6396,7 @@
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46228.13982638889</v>
+        <v>46229.46930555555</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -6396,7 +6405,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PET-99222</t>
+          <t>BEA-81012</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -6408,20 +6417,20 @@
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46228.18297453703</v>
+        <v>46229.48174768518</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PET-99222</t>
+          <t>APP-83474</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
@@ -6429,7 +6438,7 @@
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46228.50690972222</v>
+        <v>46229.58386574074</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -6438,7 +6447,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>HEA-64165</t>
+          <t>BEA-81012</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -6450,7 +6459,7 @@
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46228.58369212963</v>
+        <v>46229.63415509259</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -6459,40 +6468,40 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BEA-48693</t>
+          <t>HOM-59761</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46228.59902777777</v>
+        <v>46229.7690162037</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>HOM-31415</t>
+          <t>GAR-82396</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46228.65982638889</v>
+        <v>46229.86076388889</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -6501,7 +6510,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>APP-77442</t>
+          <t>HEA-72502</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -6513,37 +6522,37 @@
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46228.83222222222</v>
+        <v>46229.89421296296</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>HOM-92315</t>
+          <t>GAR-52405</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46228.83768518519</v>
+        <v>46230.60438657407</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PET-63231</t>
+          <t>OFF-56735</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -6555,7 +6564,7 @@
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46229.3334375</v>
+        <v>46230.67633101852</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -6564,28 +6573,28 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>TOY-31935</t>
+          <t>HOM-90449</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46229.46930555555</v>
+        <v>46230.80672453704</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>BEA-81012</t>
+          <t>PET-21419</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6597,20 +6606,20 @@
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46229.48174768518</v>
+        <v>46230.8089699074</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>APP-83474</t>
+          <t>BEA-44522</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -6618,16 +6627,16 @@
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46229.58386574074</v>
+        <v>46230.90469907408</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>BEA-81012</t>
+          <t>BEA-99656</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6639,7 +6648,7 @@
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46229.63415509259</v>
+        <v>46230.90971064815</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -6648,19 +6657,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>HOM-59761</t>
+          <t>PET-21419</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46229.71833333333</v>
+        <v>46230.91211805555</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -6669,7 +6678,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>GAR-82396</t>
+          <t>BEA-43371</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6681,16 +6690,16 @@
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46229.7690162037</v>
+        <v>46230.945</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>GAR-82396</t>
+          <t>BEA-45795</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6702,16 +6711,16 @@
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46229.86076388889</v>
+        <v>46231.47892361111</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>HEA-72502</t>
+          <t>TOY-10412</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6723,16 +6732,16 @@
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46229.89421296296</v>
+        <v>46231.49721064815</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>GAR-52405</t>
+          <t>TOY-46270</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6744,16 +6753,16 @@
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46230.60438657407</v>
+        <v>46231.76974537037</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>OFF-56735</t>
+          <t>HOM-42167</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6765,28 +6774,28 @@
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>46230.67633101852</v>
+        <v>46231.78710648148</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>HOM-90449</t>
+          <t>TOY-10412</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
-        <v>46230.80672453704</v>
+        <v>46232.38743055556</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -6795,7 +6804,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PET-21419</t>
+          <t>BEA-87172</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6807,7 +6816,7 @@
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
-        <v>46230.90469907408</v>
+        <v>46232.44763888889</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -6816,7 +6825,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BEA-99656</t>
+          <t>TEC-10470</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6828,16 +6837,16 @@
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
-        <v>46230.90971064815</v>
+        <v>46232.46537037037</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PET-21419</t>
+          <t>BEA-87172</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6849,20 +6858,20 @@
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
-        <v>46230.91211805555</v>
+        <v>46232.49363425926</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BEA-43371</t>
+          <t>BEA-87172</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -6870,16 +6879,16 @@
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
-        <v>46230.945</v>
+        <v>46232.57146990741</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BEA-45795</t>
+          <t>GAR-26825</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6891,20 +6900,20 @@
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
-        <v>46231.47892361111</v>
+        <v>46232.60127314815</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>TOY-10412</t>
+          <t>HOM-84795</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -6912,16 +6921,16 @@
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
-        <v>46231.49721064815</v>
+        <v>46232.85700231481</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>TOY-46270</t>
+          <t>APP-18249</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6933,16 +6942,16 @@
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
-        <v>46231.66956018518</v>
+        <v>46232.86006944445</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SPO-87551</t>
+          <t>APP-71537</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6954,28 +6963,28 @@
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
-        <v>46231.7325462963</v>
+        <v>46232.91003472222</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>APP-94971</t>
+          <t>APP-18249</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
-        <v>46231.76974537037</v>
+        <v>46232.98825231481</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -6984,7 +6993,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>HOM-42167</t>
+          <t>APP-18249</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6996,16 +7005,16 @@
     </row>
     <row r="180">
       <c r="A180" s="3" t="n">
-        <v>46231.78710648148</v>
+        <v>46233.66184027777</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TOY-10412</t>
+          <t>HOM-31488</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -7017,28 +7026,28 @@
     </row>
     <row r="181">
       <c r="A181" s="3" t="n">
-        <v>46231.79364583334</v>
+        <v>46233.67456018519</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>HOM-17052</t>
+          <t>HOM-92692</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
-        <v>46232.38743055556</v>
+        <v>46233.79991898148</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -7047,7 +7056,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>BEA-87172</t>
+          <t>HOM-46644</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -7059,37 +7068,37 @@
     </row>
     <row r="183">
       <c r="A183" s="3" t="n">
-        <v>46232.40891203703</v>
+        <v>46233.9094212963</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>APP-18249</t>
+          <t>TOY-18030</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n">
-        <v>46232.44763888889</v>
+        <v>46234.44710648148</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>TEC-10470</t>
+          <t>OFF-77331</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -7101,7 +7110,7 @@
     </row>
     <row r="185">
       <c r="A185" s="3" t="n">
-        <v>46232.45733796297</v>
+        <v>46234.47800925926</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -7110,7 +7119,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>APP-18249</t>
+          <t>TEC-31954</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -7122,20 +7131,20 @@
     </row>
     <row r="186">
       <c r="A186" s="3" t="n">
-        <v>46232.46537037037</v>
+        <v>46234.56679398148</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>BEA-87172</t>
+          <t>TEC-84381</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
@@ -7143,16 +7152,16 @@
     </row>
     <row r="187">
       <c r="A187" s="3" t="n">
-        <v>46232.57146990741</v>
+        <v>46234.6279050926</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>GAR-26825</t>
+          <t>TEC-84381</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -7164,20 +7173,20 @@
     </row>
     <row r="188">
       <c r="A188" s="3" t="n">
-        <v>46232.60127314815</v>
+        <v>46234.70493055556</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>HOM-84795</t>
+          <t>TEC-84381</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
@@ -7185,16 +7194,16 @@
     </row>
     <row r="189">
       <c r="A189" s="3" t="n">
-        <v>46232.67467592593</v>
+        <v>46234.80364583333</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>BEA-87172</t>
+          <t>TEC-84381</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7206,7 +7215,7 @@
     </row>
     <row r="190">
       <c r="A190" s="3" t="n">
-        <v>46232.7637962963</v>
+        <v>46234.88170138889</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -7215,19 +7224,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>HOM-88530</t>
+          <t>SPO-66554</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n">
-        <v>46232.78447916666</v>
+        <v>46234.9411574074</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -7236,7 +7245,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>APP-18249</t>
+          <t>TEC-84381</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7248,7 +7257,7 @@
     </row>
     <row r="192">
       <c r="A192" s="3" t="n">
-        <v>46232.83519675926</v>
+        <v>46235.5109375</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -7257,7 +7266,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>APP-18249</t>
+          <t>HOM-57767</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7269,16 +7278,16 @@
     </row>
     <row r="193">
       <c r="A193" s="3" t="n">
-        <v>46232.86006944445</v>
+        <v>46235.83221064815</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>APP-71537</t>
+          <t>GAR-63442</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7290,16 +7299,16 @@
     </row>
     <row r="194">
       <c r="A194" s="3" t="n">
-        <v>46232.98825231481</v>
+        <v>46235.87835648148</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>APP-18249</t>
+          <t>GAR-63442</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7311,16 +7320,16 @@
     </row>
     <row r="195">
       <c r="A195" s="3" t="n">
-        <v>46233.66184027777</v>
+        <v>46236.78042824074</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>HOM-31488</t>
+          <t>TEC-75574</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7332,16 +7341,16 @@
     </row>
     <row r="196">
       <c r="A196" s="3" t="n">
-        <v>46233.67456018519</v>
+        <v>46236.80494212963</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>HOM-92692</t>
+          <t>APP-80734</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7353,16 +7362,16 @@
     </row>
     <row r="197">
       <c r="A197" s="3" t="n">
-        <v>46233.79991898148</v>
+        <v>46236.86204861111</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>HOM-46644</t>
+          <t>SPO-97569</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7374,28 +7383,28 @@
     </row>
     <row r="198">
       <c r="A198" s="3" t="n">
-        <v>46233.9094212963</v>
+        <v>46237.70190972222</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TOY-18030</t>
+          <t>HOM-55505</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n">
-        <v>46234.44710648148</v>
+        <v>46237.79871527778</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -7404,7 +7413,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>OFF-77331</t>
+          <t>APP-23229</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7416,16 +7425,16 @@
     </row>
     <row r="200">
       <c r="A200" s="3" t="n">
-        <v>46234.47800925926</v>
+        <v>46237.82018518518</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TEC-31954</t>
+          <t>TEC-21959</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7437,7 +7446,7 @@
     </row>
     <row r="201">
       <c r="A201" s="3" t="n">
-        <v>46234.84895833334</v>
+        <v>46237.8721875</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -7446,7 +7455,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>HEA-17088</t>
+          <t>APP-87528</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7458,7 +7467,7 @@
     </row>
     <row r="202">
       <c r="A202" s="3" t="n">
-        <v>46234.88170138889</v>
+        <v>46237.91952546296</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -7467,28 +7476,28 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SPO-66554</t>
+          <t>TEC-21959</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n">
-        <v>46235.5109375</v>
+        <v>46238.79170138889</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>HOM-57767</t>
+          <t>HOM-52833</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7500,7 +7509,7 @@
     </row>
     <row r="204">
       <c r="A204" s="3" t="n">
-        <v>46235.83221064815</v>
+        <v>46238.85803240741</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -7509,7 +7518,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>GAR-63442</t>
+          <t>HOM-52833</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7521,20 +7530,20 @@
     </row>
     <row r="205">
       <c r="A205" s="3" t="n">
-        <v>46235.87835648148</v>
+        <v>46238.93766203704</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>GAR-63442</t>
+          <t>HOM-52833</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
@@ -7542,16 +7551,16 @@
     </row>
     <row r="206">
       <c r="A206" s="3" t="n">
-        <v>46236.78042824074</v>
+        <v>46241.66927083334</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>TEC-75574</t>
+          <t>BEA-46630</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7563,16 +7572,16 @@
     </row>
     <row r="207">
       <c r="A207" s="3" t="n">
-        <v>46236.80494212963</v>
+        <v>46241.80278935185</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>APP-80734</t>
+          <t>BEA-70855</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7584,16 +7593,16 @@
     </row>
     <row r="208">
       <c r="A208" s="3" t="n">
-        <v>46237.6978125</v>
+        <v>46241.87041666666</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>HOM-55505</t>
+          <t>TEC-55338</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7605,16 +7614,16 @@
     </row>
     <row r="209">
       <c r="A209" s="3" t="n">
-        <v>46237.70190972222</v>
+        <v>46241.8734837963</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>HOM-55505</t>
+          <t>HOM-24730</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7626,7 +7635,7 @@
     </row>
     <row r="210">
       <c r="A210" s="3" t="n">
-        <v>46237.79871527778</v>
+        <v>46241.91010416667</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -7635,19 +7644,19 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>APP-23229</t>
+          <t>APP-88874</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n">
-        <v>46237.82018518518</v>
+        <v>46242.41699074074</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -7656,7 +7665,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>TEC-21959</t>
+          <t>APP-43237</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7668,16 +7677,16 @@
     </row>
     <row r="212">
       <c r="A212" s="3" t="n">
-        <v>46237.8721875</v>
+        <v>46242.68912037037</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>APP-87528</t>
+          <t>OFF-34967</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7689,28 +7698,28 @@
     </row>
     <row r="213">
       <c r="A213" s="3" t="n">
-        <v>46237.91952546296</v>
+        <v>46243.46236111111</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>TEC-21959</t>
+          <t>HEA-72357</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="n">
-        <v>46238.79170138889</v>
+        <v>46243.76186342593</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -7719,7 +7728,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>HOM-52833</t>
+          <t>HEA-72981</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7731,16 +7740,16 @@
     </row>
     <row r="215">
       <c r="A215" s="3" t="n">
-        <v>46238.85803240741</v>
+        <v>46243.85148148148</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>HOM-52833</t>
+          <t>HOM-64386</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7752,7 +7761,7 @@
     </row>
     <row r="216">
       <c r="A216" s="3" t="n">
-        <v>46238.93766203704</v>
+        <v>46244.75303240741</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -7761,11 +7770,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>HOM-52833</t>
+          <t>APP-48521</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
@@ -7773,16 +7782,16 @@
     </row>
     <row r="217">
       <c r="A217" s="3" t="n">
-        <v>46241.63575231482</v>
+        <v>46244.95229166667</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>TOY-76401</t>
+          <t>SPO-73706</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -7794,7 +7803,7 @@
     </row>
     <row r="218">
       <c r="A218" s="3" t="n">
-        <v>46241.66927083334</v>
+        <v>46245.48297453704</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -7803,11 +7812,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>BEA-46630</t>
+          <t>HOM-69075</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E218" t="n">
         <v>0</v>
@@ -7815,7 +7824,7 @@
     </row>
     <row r="219">
       <c r="A219" s="3" t="n">
-        <v>46241.80278935185</v>
+        <v>46246.6356712963</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -7824,7 +7833,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BEA-70855</t>
+          <t>TEC-44842</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -7836,16 +7845,16 @@
     </row>
     <row r="220">
       <c r="A220" s="3" t="n">
-        <v>46241.87041666666</v>
+        <v>46246.66284722222</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>TEC-55338</t>
+          <t>HOM-61349</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -7857,16 +7866,16 @@
     </row>
     <row r="221">
       <c r="A221" s="3" t="n">
-        <v>46241.8734837963</v>
+        <v>46246.80615740741</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>HOM-24730</t>
+          <t>HOM-61349</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -7878,7 +7887,7 @@
     </row>
     <row r="222">
       <c r="A222" s="3" t="n">
-        <v>46241.91010416667</v>
+        <v>46246.85045138889</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -7887,28 +7896,28 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>APP-88874</t>
+          <t>PET-82682</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="3" t="n">
-        <v>46242.41699074074</v>
+        <v>46246.8903125</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>APP-43237</t>
+          <t>APP-47734</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -7920,7 +7929,7 @@
     </row>
     <row r="224">
       <c r="A224" s="3" t="n">
-        <v>46242.68912037037</v>
+        <v>46248.63248842592</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -7929,28 +7938,28 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>OFF-34967</t>
+          <t>SPO-98603</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="3" t="n">
-        <v>46243.46236111111</v>
+        <v>46249.6427662037</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>MKA</t>
+          <t>MKB</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>HEA-72357</t>
+          <t>TOY-18677</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -7962,7 +7971,7 @@
     </row>
     <row r="226">
       <c r="A226" s="3" t="n">
-        <v>46243.76186342593</v>
+        <v>46251.88578703703</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -7971,7 +7980,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>HEA-72981</t>
+          <t>HOM-51348</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -7983,7 +7992,7 @@
     </row>
     <row r="227">
       <c r="A227" s="3" t="n">
-        <v>46243.85148148148</v>
+        <v>46252.56491898148</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -7992,7 +8001,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>HOM-64386</t>
+          <t>TEC-46743</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8004,16 +8013,16 @@
     </row>
     <row r="228">
       <c r="A228" s="3" t="n">
-        <v>46244.75303240741</v>
+        <v>46252.78939814815</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>APP-48521</t>
+          <t>PET-13410</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8025,7 +8034,7 @@
     </row>
     <row r="229">
       <c r="A229" s="3" t="n">
-        <v>46244.95229166667</v>
+        <v>46253.84681712963</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -8034,7 +8043,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>SPO-73706</t>
+          <t>BEA-91613</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8046,7 +8055,7 @@
     </row>
     <row r="230">
       <c r="A230" s="3" t="n">
-        <v>46245.46832175926</v>
+        <v>46253.9346412037</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -8055,7 +8064,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>HOM-69075</t>
+          <t>GAR-21599</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8067,16 +8076,16 @@
     </row>
     <row r="231">
       <c r="A231" s="3" t="n">
-        <v>46245.8706712963</v>
+        <v>46255.82412037037</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>HOM-69075</t>
+          <t>TEC-85246</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8088,16 +8097,16 @@
     </row>
     <row r="232">
       <c r="A232" s="3" t="n">
-        <v>46246.6356712963</v>
+        <v>46255.8483449074</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>TEC-44842</t>
+          <t>TEC-85246</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8109,7 +8118,7 @@
     </row>
     <row r="233">
       <c r="A233" s="3" t="n">
-        <v>46246.66284722222</v>
+        <v>46257.70395833333</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -8118,7 +8127,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>HOM-61349</t>
+          <t>BEA-90677</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8130,16 +8139,16 @@
     </row>
     <row r="234">
       <c r="A234" s="3" t="n">
-        <v>46246.80615740741</v>
+        <v>46258.64458333333</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MKB</t>
+          <t>WEB</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>HOM-61349</t>
+          <t>PET-90822</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8151,28 +8160,28 @@
     </row>
     <row r="235">
       <c r="A235" s="3" t="n">
-        <v>46246.85045138889</v>
+        <v>46258.71694444444</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>PET-82682</t>
+          <t>SPO-76571</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="n">
-        <v>46246.8903125</v>
+        <v>46259.62512731482</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -8181,19 +8190,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>APP-47734</t>
+          <t>APP-66231</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="3" t="n">
-        <v>46248.63248842592</v>
+        <v>46259.83806712963</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -8202,7 +8211,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>SPO-98603</t>
+          <t>BEA-73004</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8214,7 +8223,7 @@
     </row>
     <row r="238">
       <c r="A238" s="3" t="n">
-        <v>46249.6427662037</v>
+        <v>46261.95210648148</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -8223,28 +8232,28 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>TOY-18677</t>
+          <t>HOM-30879</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="3" t="n">
-        <v>46251.88578703703</v>
+        <v>46262.55337962963</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>MKA</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>HOM-51348</t>
+          <t>HOM-49381</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8256,7 +8265,7 @@
     </row>
     <row r="240">
       <c r="A240" s="3" t="n">
-        <v>46252.56491898148</v>
+        <v>46262.71818287037</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -8265,392 +8274,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>TEC-46743</t>
+          <t>HOM-49381</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E240" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="3" t="n">
-        <v>46252.78939814815</v>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>PET-13410</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>1</v>
-      </c>
-      <c r="E241" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="3" t="n">
-        <v>46253.84681712963</v>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>BEA-91613</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>1</v>
-      </c>
-      <c r="E242" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="3" t="n">
-        <v>46253.89300925926</v>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>BEA-43568</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>3</v>
-      </c>
-      <c r="E243" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="3" t="n">
-        <v>46253.9346412037</v>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>GAR-21599</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>1</v>
-      </c>
-      <c r="E244" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="3" t="n">
-        <v>46255.82412037037</v>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>TEC-85246</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>1</v>
-      </c>
-      <c r="E245" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="3" t="n">
-        <v>46255.8483449074</v>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>TEC-85246</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>1</v>
-      </c>
-      <c r="E246" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="3" t="n">
-        <v>46257.70395833333</v>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>BEA-90677</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>1</v>
-      </c>
-      <c r="E247" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="3" t="n">
-        <v>46257.96581018518</v>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>SPO-11580</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>1</v>
-      </c>
-      <c r="E248" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="3" t="n">
-        <v>46257.99844907408</v>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>SPO-11580</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>1</v>
-      </c>
-      <c r="E249" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="3" t="n">
-        <v>46258.64458333333</v>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>PET-90822</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
-        <v>1</v>
-      </c>
-      <c r="E250" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="3" t="n">
-        <v>46258.71694444444</v>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>SPO-76571</t>
-        </is>
-      </c>
-      <c r="D251" t="n">
-        <v>2</v>
-      </c>
-      <c r="E251" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="3" t="n">
-        <v>46259.62512731482</v>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>APP-66231</t>
-        </is>
-      </c>
-      <c r="D252" t="n">
-        <v>3</v>
-      </c>
-      <c r="E252" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="3" t="n">
-        <v>46259.83806712963</v>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>BEA-73004</t>
-        </is>
-      </c>
-      <c r="D253" t="n">
-        <v>2</v>
-      </c>
-      <c r="E253" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="3" t="n">
-        <v>46259.96693287037</v>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>TOY-88371</t>
-        </is>
-      </c>
-      <c r="D254" t="n">
-        <v>1</v>
-      </c>
-      <c r="E254" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="3" t="n">
-        <v>46261.64368055556</v>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>HOM-30879</t>
-        </is>
-      </c>
-      <c r="D255" t="n">
-        <v>1</v>
-      </c>
-      <c r="E255" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="3" t="n">
-        <v>46261.95210648148</v>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>HOM-30879</t>
-        </is>
-      </c>
-      <c r="D256" t="n">
-        <v>1</v>
-      </c>
-      <c r="E256" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="3" t="n">
-        <v>46262.55337962963</v>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>MKA</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>HOM-49381</t>
-        </is>
-      </c>
-      <c r="D257" t="n">
-        <v>1</v>
-      </c>
-      <c r="E257" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="3" t="n">
-        <v>46263.5819212963</v>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>MKB</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>HOM-34353</t>
-        </is>
-      </c>
-      <c r="D258" t="n">
-        <v>2</v>
-      </c>
-      <c r="E258" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
